--- a/gte/nodes/HPT/turbine_stage_1_blade_rotor_coordinates_lattice.xlsx
+++ b/gte/nodes/HPT/turbine_stage_1_blade_rotor_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-15.321497455914416</v>
+        <v>-15.326714651544165</v>
       </c>
       <c r="B1">
-        <v>11.256903306360931</v>
+        <v>11.233594226746778</v>
       </c>
       <c r="C1">
         <v>324.98254890622445</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-18.039724927897563</v>
+        <v>-18.037319048129579</v>
       </c>
       <c r="B2">
-        <v>9.1295017318633143</v>
+        <v>9.1035648633695985</v>
       </c>
       <c r="C2">
         <v>324.98254890622445</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-19.568432687028459</v>
+        <v>-19.560953438309511</v>
       </c>
       <c r="B3">
-        <v>7.4805238444678412</v>
+        <v>7.4532132129869257</v>
       </c>
       <c r="C3">
         <v>324.98254890622445</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-20.727903268648973</v>
+        <v>-20.716351908332147</v>
       </c>
       <c r="B4">
-        <v>5.9800527955644558</v>
+        <v>5.9516728746595442</v>
       </c>
       <c r="C4">
         <v>324.98254890622445</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-21.636304537879326</v>
+        <v>-21.621288257908628</v>
       </c>
       <c r="B5">
-        <v>4.5805615831901205</v>
+        <v>4.5513491605762715</v>
       </c>
       <c r="C5">
         <v>324.98254890622445</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-22.362209505352098</v>
+        <v>-22.344120305218546</v>
       </c>
       <c r="B6">
-        <v>3.2544702082678367</v>
+        <v>3.22461734415367</v>
       </c>
       <c r="C6">
         <v>324.98254890622445</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-22.935331991656664</v>
+        <v>-22.914467483392283</v>
       </c>
       <c r="B7">
-        <v>1.9898278006685388</v>
+        <v>1.9595076351969629</v>
       </c>
       <c r="C7">
         <v>324.98254890622445</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-23.390088940297048</v>
+        <v>-23.366660519386645</v>
       </c>
       <c r="B8">
-        <v>0.7727918987397876</v>
+        <v>0.7421463178555292</v>
       </c>
       <c r="C8">
         <v>324.98254890622445</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-23.739731914082704</v>
+        <v>-23.713914858230918</v>
       </c>
       <c r="B9">
-        <v>-0.401967263364807</v>
+        <v>-0.43280722676887312</v>
       </c>
       <c r="C9">
         <v>324.98254890622445</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-23.995295791266198</v>
+        <v>-23.96723771574683</v>
       </c>
       <c r="B10">
-        <v>-1.5388879030898763</v>
+        <v>-1.5698012291145111</v>
       </c>
       <c r="C10">
         <v>324.98254890622445</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-24.166025456431228</v>
+        <v>-24.135852605888761</v>
       </c>
       <c r="B11">
-        <v>-2.6416883041440316</v>
+        <v>-2.6725630909316669</v>
       </c>
       <c r="C11">
         <v>324.98254890622445</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-24.259708669151234</v>
+        <v>-24.227530623903853</v>
       </c>
       <c r="B12">
-        <v>-3.71350069595494</v>
+        <v>-3.7442332632641757</v>
       </c>
       <c r="C12">
         <v>324.98254890622445</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-24.282937877772842</v>
+        <v>-24.248851100517108</v>
       </c>
       <c r="B13">
-        <v>-4.7569765549218177</v>
+        <v>-4.787470581885616</v>
       </c>
       <c r="C13">
         <v>324.98254890622445</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-24.241318520630717</v>
+        <v>-24.205409052080547</v>
       </c>
       <c r="B14">
-        <v>-5.7743703829641415</v>
+        <v>-5.8045361019477</v>
       </c>
       <c r="C14">
         <v>324.98254890622445</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-24.139637603887032</v>
+        <v>-24.101983128148746</v>
       </c>
       <c r="B15">
-        <v>-6.7676075093669628</v>
+        <v>-6.797360968868734</v>
       </c>
       <c r="C15">
         <v>324.98254890622445</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-23.982003600757182</v>
+        <v>-23.942675036397084</v>
       </c>
       <c r="B16">
-        <v>-7.73834035811521</v>
+        <v>-7.76760276266041</v>
       </c>
       <c r="C16">
         <v>324.98254890622445</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-23.771966776402554</v>
+        <v>-23.731029500883544</v>
       </c>
       <c r="B17">
-        <v>-8.687996842450131</v>
+        <v>-8.7166939753993287</v>
       </c>
       <c r="C17">
         <v>324.98254890622445</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-23.512627835117506</v>
+        <v>-23.470142613144052</v>
       </c>
       <c r="B18">
-        <v>-9.61782406266362</v>
+        <v>-9.6458857980163089</v>
       </c>
       <c r="C18">
         <v>324.98254890622445</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-23.190512922456467</v>
+        <v>-23.146556216623321</v>
       </c>
       <c r="B19">
-        <v>-10.52240284742655</v>
+        <v>-10.549739527155138</v>
       </c>
       <c r="C19">
         <v>324.98254890622445</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-22.821551054230106</v>
+        <v>-22.776179552199796</v>
       </c>
       <c r="B20">
-        <v>-11.408139831613235</v>
+        <v>-11.434684397117332</v>
       </c>
       <c r="C20">
         <v>324.98254890622445</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-22.40855725349596</v>
+        <v>-22.361824210258209</v>
       </c>
       <c r="B21">
-        <v>-12.27616721479626</v>
+        <v>-12.301856626373736</v>
       </c>
       <c r="C21">
         <v>324.98254890622445</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-21.953359874792085</v>
+        <v>-21.905316364942522</v>
       </c>
       <c r="B22">
-        <v>-13.12722035941642</v>
+        <v>-13.151994207487086</v>
       </c>
       <c r="C22">
         <v>324.98254890622445</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-21.441428700352962</v>
+        <v>-21.392143695561632</v>
       </c>
       <c r="B23">
-        <v>-13.95545522583094</v>
+        <v>-13.979232428828789</v>
       </c>
       <c r="C23">
         <v>324.98254890622445</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-20.880899068449118</v>
+        <v>-20.830432378077539</v>
       </c>
       <c r="B24">
-        <v>-14.764143839285939</v>
+        <v>-14.786855236479884</v>
       </c>
       <c r="C24">
         <v>324.98254890622445</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-20.279784815094636</v>
+        <v>-20.228186983883589</v>
       </c>
       <c r="B25">
-        <v>-15.556509356936582</v>
+        <v>-15.578097433745201</v>
       </c>
       <c r="C25">
         <v>324.98254890622445</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-19.636015295849369</v>
+        <v>-19.583339869298779</v>
       </c>
       <c r="B26">
-        <v>-16.331718967575931</v>
+        <v>-16.352123445515993</v>
       </c>
       <c r="C26">
         <v>324.98254890622445</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-18.925612164982006</v>
+        <v>-18.871945194862253</v>
       </c>
       <c r="B27">
-        <v>-17.080128603559341</v>
+        <v>-17.099256291374605</v>
       </c>
       <c r="C27">
         <v>324.98254890622445</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-18.17327004903208</v>
+        <v>-18.118667638172859</v>
       </c>
       <c r="B28">
-        <v>-17.811670419985223</v>
+        <v>-17.829463448240027</v>
       </c>
       <c r="C28">
         <v>324.98254890622445</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-17.379854673839748</v>
+        <v>-17.324372307034849</v>
       </c>
       <c r="B29">
-        <v>-18.52669261095577</v>
+        <v>-18.54309452303643</v>
       </c>
       <c r="C29">
         <v>324.98254890622445</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-16.511868235005409</v>
+        <v>-16.455611065979223</v>
       </c>
       <c r="B30">
-        <v>-19.211722391684379</v>
+        <v>-19.226632472334654</v>
       </c>
       <c r="C30">
         <v>324.98254890622445</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-15.590998479695914</v>
+        <v>-15.534045979860094</v>
       </c>
       <c r="B31">
-        <v>-19.875482553271013</v>
+        <v>-19.888831358724211</v>
       </c>
       <c r="C31">
         <v>324.98254890622445</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-14.623382023940337</v>
+        <v>-14.56580588374119</v>
       </c>
       <c r="B32">
-        <v>-20.520441236794163</v>
+        <v>-20.532167963902062</v>
       </c>
       <c r="C32">
         <v>324.98254890622445</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-13.567425673739759</v>
+        <v>-13.50936983106663</v>
       </c>
       <c r="B33">
-        <v>-21.129869699538339</v>
+        <v>-21.139862864144089</v>
       </c>
       <c r="C33">
         <v>324.98254890622445</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-12.439855146576509</v>
+        <v>-12.381448956828924</v>
       </c>
       <c r="B34">
-        <v>-21.710495009025713</v>
+        <v>-21.718669354791786</v>
       </c>
       <c r="C34">
         <v>324.98254890622445</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-11.252577031989686</v>
+        <v>-11.193932199661987</v>
       </c>
       <c r="B35">
-        <v>-22.267105984143914</v>
+        <v>-22.273391987656115</v>
       </c>
       <c r="C35">
         <v>324.98254890622445</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-9.938769585993386</v>
+        <v>-9.88014718784621</v>
       </c>
       <c r="B36">
-        <v>-22.772826983580792</v>
+        <v>-22.777087157916583</v>
       </c>
       <c r="C36">
         <v>324.98254890622445</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-8.5175899176049175</v>
+        <v>-8.4592542341406016</v>
       </c>
       <c r="B37">
-        <v>-23.235362978200872</v>
+        <v>-23.23749792138328</v>
       </c>
       <c r="C37">
         <v>324.98254890622445</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-7.0048938596160166</v>
+        <v>-6.9470811687044085</v>
       </c>
       <c r="B38">
-        <v>-23.661091168738469</v>
+        <v>-23.661020612699438</v>
       </c>
       <c r="C38">
         <v>324.98254890622445</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-5.24884833763526</v>
+        <v>-5.1923244769945995</v>
       </c>
       <c r="B39">
-        <v>-23.988944438365213</v>
+        <v>-23.986510532814229</v>
       </c>
       <c r="C39">
         <v>324.98254890622445</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-3.4928028156545019</v>
+        <v>-3.4375677852847892</v>
       </c>
       <c r="B40">
-        <v>-24.316797707991967</v>
+        <v>-24.312000452929006</v>
       </c>
       <c r="C40">
         <v>324.98254890622445</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-1.7367572936737556</v>
+        <v>-1.6828110935749892</v>
       </c>
       <c r="B41">
-        <v>-24.64465097761871</v>
+        <v>-24.637490373043796</v>
       </c>
       <c r="C41">
         <v>324.98254890622445</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-1.5858398081099943</v>
+        <v>-1.5320233433969606</v>
       </c>
       <c r="B42">
-        <v>-24.583952109738266</v>
+        <v>-24.576554104424826</v>
       </c>
       <c r="C42">
         <v>324.98254890622445</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-3.0117263295326611</v>
+        <v>-2.9569048539161371</v>
       </c>
       <c r="B43">
-        <v>-24.123309206892078</v>
+        <v>-24.117755194501321</v>
       </c>
       <c r="C43">
         <v>324.98254890622445</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-4.437612850955337</v>
+        <v>-4.38178636443532</v>
       </c>
       <c r="B44">
-        <v>-23.662666304045874</v>
+        <v>-23.658956284577819</v>
       </c>
       <c r="C44">
         <v>324.98254890622445</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-5.8634993723780138</v>
+        <v>-5.8066678749545044</v>
       </c>
       <c r="B45">
-        <v>-23.202023401199678</v>
+        <v>-23.200157374654307</v>
       </c>
       <c r="C45">
         <v>324.98254890622445</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-7.05962357288539</v>
+        <v>-7.0025412221638721</v>
       </c>
       <c r="B46">
-        <v>-22.648970313350439</v>
+        <v>-22.648811802691558</v>
       </c>
       <c r="C46">
         <v>324.98254890622445</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-8.1707637163398488</v>
+        <v>-8.1136611747064542</v>
       </c>
       <c r="B47">
-        <v>-22.061736719301216</v>
+        <v>-22.063215732145949</v>
       </c>
       <c r="C47">
         <v>324.98254890622445</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-9.1825514353276017</v>
+        <v>-9.1256860891095251</v>
       </c>
       <c r="B48">
-        <v>-21.434543675465385</v>
+        <v>-21.437573425379256</v>
       </c>
       <c r="C48">
         <v>324.98254890622445</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-10.079477976519881</v>
+        <v>-10.023100872013739</v>
       </c>
       <c r="B49">
-        <v>-20.761153576135584</v>
+        <v>-20.765614930784146</v>
       </c>
       <c r="C49">
         <v>324.98254890622445</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-10.922952268206224</v>
+        <v>-10.867169732539534</v>
       </c>
       <c r="B50">
-        <v>-20.066265033344745</v>
+        <v>-20.072098309272619</v>
       </c>
       <c r="C50">
         <v>324.98254890622445</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-11.702616597711762</v>
+        <v>-11.647551277433786</v>
       </c>
       <c r="B51">
-        <v>-19.345712184993825</v>
+        <v>-19.352844402282916</v>
       </c>
       <c r="C51">
         <v>324.98254890622445</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-12.405040406759074</v>
+        <v>-12.350826698243415</v>
       </c>
       <c r="B52">
-        <v>-18.594093273430971</v>
+        <v>-18.602430407793786</v>
       </c>
       <c r="C52">
         <v>324.98254890622445</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-13.067199760103565</v>
+        <v>-13.013903781370496</v>
       </c>
       <c r="B53">
-        <v>-17.826280036420318</v>
+        <v>-17.835771481603206</v>
       </c>
       <c r="C53">
         <v>324.98254890622445</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-13.684030662393546</v>
+        <v>-13.631725390356273</v>
       </c>
       <c r="B54">
-        <v>-17.04023573989058</v>
+        <v>-17.050823936307296</v>
       </c>
       <c r="C54">
         <v>324.98254890622445</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-14.238306107006743</v>
+        <v>-14.187086366240106</v>
       </c>
       <c r="B55">
-        <v>-16.229031698308507</v>
+        <v>-16.2406348318508</v>
       </c>
       <c r="C55">
         <v>324.98254890622445</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-14.758825325811676</v>
+        <v>-14.708740311061954</v>
       </c>
       <c r="B56">
-        <v>-15.404250935097231</v>
+        <v>-15.416824059210278</v>
       </c>
       <c r="C56">
         <v>324.98254890622445</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-15.245057472720394</v>
+        <v>-15.196156708892236</v>
       </c>
       <c r="B57">
-        <v>-14.565679944469556</v>
+        <v>-14.579177226559118</v>
       </c>
       <c r="C57">
         <v>324.98254890622445</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-15.678112594063705</v>
+        <v>-15.630470565047361</v>
       </c>
       <c r="B58">
-        <v>-13.705721205185647</v>
+        <v>-13.720070621877092</v>
       </c>
       <c r="C58">
         <v>324.98254890622445</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-16.078091280076869</v>
+        <v>-16.031753296983297</v>
       </c>
       <c r="B59">
-        <v>-12.832459155350533</v>
+        <v>-12.847615496139273</v>
       </c>
       <c r="C59">
         <v>324.98254890622445</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-16.446987816091028</v>
+        <v>-16.401996254913737</v>
       </c>
       <c r="B60">
-        <v>-11.946695894610786</v>
+        <v>-11.962616592777357</v>
       </c>
       <c r="C60">
         <v>324.98254890622445</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-16.779357783423986</v>
+        <v>-16.735762075991747</v>
       </c>
       <c r="B61">
-        <v>-11.046241682996635</v>
+        <v>-11.062876567493625</v>
       </c>
       <c r="C61">
         <v>324.98254890622445</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-17.0704884132311</v>
+        <v>-17.02834421148825</v>
       </c>
       <c r="B62">
-        <v>-10.129201049400914</v>
+        <v>-10.146493412218559</v>
       </c>
       <c r="C62">
         <v>324.98254890622445</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-17.331828838797968</v>
+        <v>-17.291176546251741</v>
       </c>
       <c r="B63">
-        <v>-9.2001788242450377</v>
+        <v>-9.2180877826596941</v>
       </c>
       <c r="C63">
         <v>324.98254890622445</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-17.562678129330937</v>
+        <v>-17.523559360699039</v>
       </c>
       <c r="B64">
-        <v>-8.2588930938363863</v>
+        <v>-8.2773769084963043</v>
       </c>
       <c r="C64">
         <v>324.98254890622445</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-17.761830427641474</v>
+        <v>-17.724288847003841</v>
       </c>
       <c r="B65">
-        <v>-7.3048588635708143</v>
+        <v>-7.3238743075242168</v>
       </c>
       <c r="C65">
         <v>324.98254890622445</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-17.920057052897896</v>
+        <v>-17.884150339360602</v>
       </c>
       <c r="B66">
-        <v>-6.3343643668732206</v>
+        <v>-6.3538561537025355</v>
       </c>
       <c r="C66">
         <v>324.98254890622445</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-18.047297116762913</v>
+        <v>-18.013070290163931</v>
       </c>
       <c r="B67">
-        <v>-5.3514071049172456</v>
+        <v>-5.3713339199051369</v>
       </c>
       <c r="C67">
         <v>324.98254890622445</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-18.142444894049781</v>
+        <v>-18.1099458720127</v>
       </c>
       <c r="B68">
-        <v>-4.35554235609379</v>
+        <v>-4.3758619320857122</v>
       </c>
       <c r="C68">
         <v>324.98254890622445</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-18.204273068453286</v>
+        <v>-18.1735533127949</v>
       </c>
       <c r="B69">
-        <v>-3.3462764949625603</v>
+        <v>-3.3669456400831379</v>
       </c>
       <c r="C69">
         <v>324.98254890622445</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-18.231375969599888</v>
+        <v>-18.202491384227425</v>
       </c>
       <c r="B70">
-        <v>-2.3230441622481437</v>
+        <v>-2.344018780239026</v>
       </c>
       <c r="C70">
         <v>324.98254890622445</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-18.222110734566218</v>
+        <v>-18.195122877149082</v>
       </c>
       <c r="B71">
-        <v>-1.2851846000591665</v>
+        <v>-1.3064197244230142</v>
       </c>
       <c r="C71">
         <v>324.98254890622445</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-18.174535316110685</v>
+        <v>-18.149513017086921</v>
       </c>
       <c r="B72">
-        <v>-0.23191671885855991</v>
+        <v>-0.25336659256286737</v>
       </c>
       <c r="C72">
         <v>324.98254890622445</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-18.086344482232107</v>
+        <v>-18.063366004179475</v>
       </c>
       <c r="B73">
-        <v>0.83768664345255406</v>
+        <v>0.81606839280932986</v>
       </c>
       <c r="C73">
         <v>324.98254890622445</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-17.954808122753381</v>
+        <v>-17.933964044795442</v>
       </c>
       <c r="B74">
-        <v>1.9247235345677258</v>
+        <v>1.9029835450683208</v>
       </c>
       <c r="C74">
         <v>324.98254890622445</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-17.776721305807225</v>
+        <v>-17.758118385484789</v>
       </c>
       <c r="B75">
-        <v>3.0304829750086713</v>
+        <v>3.008667501630355</v>
       </c>
       <c r="C75">
         <v>324.98254890622445</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-17.548384310676816</v>
+        <v>-17.532150662333702</v>
       </c>
       <c r="B76">
-        <v>4.1564529888976214</v>
+        <v>4.1346067610423329</v>
       </c>
       <c r="C76">
         <v>324.98254890622445</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-17.265646306357919</v>
+        <v>-17.251938338724127</v>
       </c>
       <c r="B77">
-        <v>5.304303036481544</v>
+        <v>5.2824673206976316</v>
       </c>
       <c r="C77">
         <v>324.98254890622445</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-16.916569647553995</v>
+        <v>-16.905610661701772</v>
       </c>
       <c r="B78">
-        <v>6.4788344272438954</v>
+        <v>6.4570463832196587</v>
       </c>
       <c r="C78">
         <v>324.98254890622445</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-16.4946932993367</v>
+        <v>-16.486780994668106</v>
       </c>
       <c r="B79">
-        <v>7.6826457832331529</v>
+        <v>7.6609249129299855</v>
       </c>
       <c r="C79">
         <v>324.98254890622445</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-15.988693721643889</v>
+        <v>-15.984291775821703</v>
       </c>
       <c r="B80">
-        <v>8.920291421396783</v>
+        <v>8.8986118980074416</v>
       </c>
       <c r="C80">
         <v>324.98254890622445</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-15.40773158956261</v>
+        <v>-15.407588288380003</v>
       </c>
       <c r="B81">
-        <v>10.188086927004918</v>
+        <v>10.166290315420376</v>
       </c>
       <c r="C81">
         <v>324.98254890622445</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-15.321497455914416</v>
+        <v>-15.326714651544165</v>
       </c>
       <c r="B82">
-        <v>11.256903306360931</v>
+        <v>11.233594226746778</v>
       </c>
       <c r="C82">
         <v>324.98254890622445</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-13.623764375555046</v>
+        <v>-13.623126358575918</v>
       </c>
       <c r="B1">
-        <v>9.6992305793979039</v>
+        <v>9.6946181605383934</v>
       </c>
       <c r="C1">
         <v>339.231271826982</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-15.574350438653925</v>
+        <v>-15.573005882008578</v>
       </c>
       <c r="B2">
-        <v>7.8941251974108777</v>
+        <v>7.8894651105012592</v>
       </c>
       <c r="C2">
         <v>339.231271826982</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-16.707428359132649</v>
+        <v>-16.7055968770413</v>
       </c>
       <c r="B3">
-        <v>6.4532128056404865</v>
+        <v>6.4486007124316611</v>
       </c>
       <c r="C3">
         <v>339.231271826982</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-17.571466482072022</v>
+        <v>-17.569218570337455</v>
       </c>
       <c r="B4">
-        <v>5.1321553770746213</v>
+        <v>5.1276235524003706</v>
       </c>
       <c r="C4">
         <v>339.231271826982</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-18.246878318991744</v>
+        <v>-18.244263922775311</v>
       </c>
       <c r="B5">
-        <v>3.8951293697968459</v>
+        <v>3.8907002101055568</v>
       </c>
       <c r="C5">
         <v>339.231271826982</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-18.782315275094771</v>
+        <v>-18.779371843040053</v>
       </c>
       <c r="B6">
-        <v>2.7204609926662897</v>
+        <v>2.7161509459419322</v>
       </c>
       <c r="C6">
         <v>339.231271826982</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-19.198938214231571</v>
+        <v>-19.195697784505157</v>
       </c>
       <c r="B7">
-        <v>1.5987232591130494</v>
+        <v>1.5945461749790968</v>
       </c>
       <c r="C7">
         <v>339.231271826982</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-19.522512312231459</v>
+        <v>-19.519000137773347</v>
       </c>
       <c r="B8">
-        <v>0.51843800037092769</v>
+        <v>0.51440465275631642</v>
       </c>
       <c r="C8">
         <v>339.231271826982</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-19.76279885959017</v>
+        <v>-19.759037652245098</v>
       </c>
       <c r="B9">
-        <v>-0.52474335623926838</v>
+        <v>-0.52862337181242347</v>
       </c>
       <c r="C9">
         <v>339.231271826982</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-19.928035578452246</v>
+        <v>-19.924045885567867</v>
       </c>
       <c r="B10">
-        <v>-1.5344906465319923</v>
+        <v>-1.5382087200947756</v>
       </c>
       <c r="C10">
         <v>339.231271826982</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-20.025199148416196</v>
+        <v>-20.020999668889207</v>
       </c>
       <c r="B11">
-        <v>-2.5139119224914381</v>
+        <v>-2.5174602719393522</v>
       </c>
       <c r="C11">
         <v>339.231271826982</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-20.060218315722768</v>
+        <v>-20.055826166097933</v>
       </c>
       <c r="B12">
-        <v>-3.4656483906195183</v>
+        <v>-3.4690199322157538</v>
       </c>
       <c r="C12">
         <v>339.231271826982</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-20.03814766142936</v>
+        <v>-20.033578600539276</v>
       </c>
       <c r="B13">
-        <v>-4.391951824193602</v>
+        <v>-4.3951400657334139</v>
       </c>
       <c r="C13">
         <v>339.231271826982</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-19.963310407749198</v>
+        <v>-19.958579026657041</v>
       </c>
       <c r="B14">
-        <v>-5.29474818228751</v>
+        <v>-5.297747134607433</v>
       </c>
       <c r="C14">
         <v>339.231271826982</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-19.839417405885225</v>
+        <v>-19.834537288393417</v>
       </c>
       <c r="B15">
-        <v>-6.1756906178490842</v>
+        <v>-6.1784947213876</v>
       </c>
       <c r="C15">
         <v>339.231271826982</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-19.66966849105685</v>
+        <v>-19.664652348700503</v>
       </c>
       <c r="B16">
-        <v>-7.0362046305106789</v>
+        <v>-7.038808694492503</v>
       </c>
       <c r="C16">
         <v>339.231271826982</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-19.456841698724446</v>
+        <v>-19.45170148292733</v>
       </c>
       <c r="B17">
-        <v>-7.8775278116655771</v>
+        <v>-7.8799269642290657</v>
       </c>
       <c r="C17">
         <v>339.231271826982</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-19.203375466540265</v>
+        <v>-19.198122459407418</v>
       </c>
       <c r="B18">
-        <v>-8.7007464647445723</v>
+        <v>-8.702936113008727</v>
       </c>
       <c r="C18">
         <v>339.231271826982</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-18.897976641152187</v>
+        <v>-18.892625268904109</v>
       </c>
       <c r="B19">
-        <v>-9.50082958507154</v>
+        <v>-9.502803863853881</v>
       </c>
       <c r="C19">
         <v>339.231271826982</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-18.553689232010779</v>
+        <v>-18.548250301266219</v>
       </c>
       <c r="B20">
-        <v>-10.283588168963899</v>
+        <v>-10.285342687971562</v>
       </c>
       <c r="C20">
         <v>339.231271826982</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-18.172777036783938</v>
+        <v>-18.167260725547365</v>
       </c>
       <c r="B21">
-        <v>-11.050030719210707</v>
+        <v>-11.051561343927519</v>
       </c>
       <c r="C21">
         <v>339.231271826982</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-17.756703825776626</v>
+        <v>-17.751119905157541</v>
       </c>
       <c r="B22">
-        <v>-11.8008093331509</v>
+        <v>-11.802112094252598</v>
       </c>
       <c r="C22">
         <v>339.231271826982</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-17.293253358771963</v>
+        <v>-17.287614992166656</v>
       </c>
       <c r="B23">
-        <v>-12.530481778686907</v>
+        <v>-12.531551326618306</v>
       </c>
       <c r="C23">
         <v>339.231271826982</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-16.78912391388393</v>
+        <v>-16.783442397185972</v>
       </c>
       <c r="B24">
-        <v>-13.242032082287032</v>
+        <v>-13.242863820952199</v>
       </c>
       <c r="C24">
         <v>339.231271826982</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-16.250987022531326</v>
+        <v>-16.245271793657217</v>
       </c>
       <c r="B25">
-        <v>-13.938432354992214</v>
+        <v>-13.939022439667895</v>
       </c>
       <c r="C25">
         <v>339.231271826982</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-15.67708192851593</v>
+        <v>-15.67134291022861</v>
       </c>
       <c r="B26">
-        <v>-14.618898194750111</v>
+        <v>-14.619242579953083</v>
       </c>
       <c r="C26">
         <v>339.231271826982</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-15.04723987310433</v>
+        <v>-15.041492561450072</v>
       </c>
       <c r="B27">
-        <v>-15.274444589462208</v>
+        <v>-15.274536938803102</v>
       </c>
       <c r="C27">
         <v>339.231271826982</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-14.382182135089524</v>
+        <v>-14.376436268049771</v>
       </c>
       <c r="B28">
-        <v>-15.914302694258717</v>
+        <v>-15.914139010704451</v>
       </c>
       <c r="C28">
         <v>339.231271826982</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-13.682638247787811</v>
+        <v>-13.676903356693797</v>
       </c>
       <c r="B29">
-        <v>-16.538797510085892</v>
+        <v>-16.538373877214998</v>
       </c>
       <c r="C29">
         <v>339.231271826982</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-12.920521963451467</v>
+        <v>-12.914815301954489</v>
       </c>
       <c r="B30">
-        <v>-17.135416850192392</v>
+        <v>-17.134726144050045</v>
       </c>
       <c r="C30">
         <v>339.231271826982</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-12.11411941060137</v>
+        <v>-12.108453145845321</v>
       </c>
       <c r="B31">
-        <v>-17.712307030777772</v>
+        <v>-17.711344189560982</v>
       </c>
       <c r="C31">
         <v>339.231271826982</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-11.268604111601563</v>
+        <v>-11.262988976468808</v>
       </c>
       <c r="B32">
-        <v>-18.271772812469472</v>
+        <v>-18.270533359947166</v>
       </c>
       <c r="C32">
         <v>339.231271826982</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-10.349377877960219</v>
+        <v>-10.343834023598914</v>
       </c>
       <c r="B33">
-        <v>-18.798400993776276</v>
+        <v>-18.796876460373465</v>
       </c>
       <c r="C33">
         <v>339.231271826982</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-9.3707492418212635</v>
+        <v>-9.3652927960994941</v>
       </c>
       <c r="B34">
-        <v>-19.298565905222155</v>
+        <v>-19.296749415706064</v>
       </c>
       <c r="C34">
         <v>339.231271826982</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-8.3427109617761612</v>
+        <v>-8.3373553063463461</v>
       </c>
       <c r="B35">
-        <v>-19.776719236572887</v>
+        <v>-19.774605057491048</v>
       </c>
       <c r="C35">
         <v>339.231271826982</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-7.2107022188538386</v>
+        <v>-7.2054753021257207</v>
       </c>
       <c r="B36">
-        <v>-20.208554602639374</v>
+        <v>-20.20613057574964</v>
       </c>
       <c r="C36">
         <v>339.231271826982</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-5.99181077887027</v>
+        <v>-5.986735601791338</v>
       </c>
       <c r="B37">
-        <v>-20.601684459132088</v>
+        <v>-20.59894026660082</v>
       </c>
       <c r="C37">
         <v>339.231271826982</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-4.6992170155697934</v>
+        <v>-4.6943130040753944</v>
       </c>
       <c r="B38">
-        <v>-20.961980551512475</v>
+        <v>-20.958907402555578</v>
       </c>
       <c r="C38">
         <v>339.231271826982</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-3.21501331356291</v>
+        <v>-3.2103298964512939</v>
       </c>
       <c r="B39">
-        <v>-21.236916030469427</v>
+        <v>-21.233490592082905</v>
       </c>
       <c r="C39">
         <v>339.231271826982</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-1.7308096115560279</v>
+        <v>-1.7263467888271937</v>
       </c>
       <c r="B40">
-        <v>-21.511851509426382</v>
+        <v>-21.508073781610236</v>
       </c>
       <c r="C40">
         <v>339.231271826982</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-0.24660590954915346</v>
+        <v>-0.24236368120309804</v>
       </c>
       <c r="B41">
-        <v>-21.786786988383327</v>
+        <v>-21.782656971137563</v>
       </c>
       <c r="C41">
         <v>339.231271826982</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-0.14533381865557485</v>
+        <v>-0.14112014903252049</v>
       </c>
       <c r="B42">
-        <v>-21.741671125084629</v>
+        <v>-21.737529860486617</v>
       </c>
       <c r="C42">
         <v>339.231271826982</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-1.4079867030819051</v>
+        <v>-1.4036149163921237</v>
       </c>
       <c r="B43">
-        <v>-21.368036623410926</v>
+        <v>-21.364223042647215</v>
       </c>
       <c r="C43">
         <v>339.231271826982</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-2.6706395875082434</v>
+        <v>-2.6661096837517331</v>
       </c>
       <c r="B44">
-        <v>-20.994402121737217</v>
+        <v>-20.990916224807812</v>
       </c>
       <c r="C44">
         <v>339.231271826982</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-3.9332924719345823</v>
+        <v>-3.9286044511113416</v>
       </c>
       <c r="B45">
-        <v>-20.620767620063511</v>
+        <v>-20.617609406968409</v>
       </c>
       <c r="C45">
         <v>339.231271826982</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-5.0134529720816472</v>
+        <v>-5.0086536918401707</v>
       </c>
       <c r="B46">
-        <v>-20.165834298650324</v>
+        <v>-20.162981448987779</v>
       </c>
       <c r="C46">
         <v>339.231271826982</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-6.0242946235835886</v>
+        <v>-6.0194022737196571</v>
       </c>
       <c r="B47">
-        <v>-19.680020014161311</v>
+        <v>-19.677464223979118</v>
       </c>
       <c r="C47">
         <v>339.231271826982</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-6.9536352056164912</v>
+        <v>-6.9486712694589627</v>
       </c>
       <c r="B48">
-        <v>-19.157897689851868</v>
+        <v>-19.155629239003861</v>
       </c>
       <c r="C48">
         <v>339.231271826982</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-7.78683515515228</v>
+        <v>-7.7818253730992506</v>
       </c>
       <c r="B49">
-        <v>-18.592945523727966</v>
+        <v>-18.59095312355868</v>
       </c>
       <c r="C49">
         <v>339.231271826982</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-8.57482306020388</v>
+        <v>-8.5697796301849944</v>
       </c>
       <c r="B50">
-        <v>-18.00785177268758</v>
+        <v>-18.006130155932997</v>
       </c>
       <c r="C50">
         <v>339.231271826982</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-9.3086455248354554</v>
+        <v>-9.303583097895844</v>
       </c>
       <c r="B51">
-        <v>-17.39862777427162</v>
+        <v>-17.397170647319786</v>
       </c>
       <c r="C51">
         <v>339.231271826982</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-9.9762052097364524</v>
+        <v>-9.9711418366450655</v>
       </c>
       <c r="B52">
-        <v>-16.759884265734577</v>
+        <v>-16.75868398620802</v>
       </c>
       <c r="C52">
         <v>339.231271826982</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-10.609002012099506</v>
+        <v>-10.603947199077462</v>
       </c>
       <c r="B53">
-        <v>-16.105654185896281</v>
+        <v>-16.104706760662957</v>
       </c>
       <c r="C53">
         <v>339.231271826982</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-11.202582183934826</v>
+        <v>-11.197546668488439</v>
       </c>
       <c r="B54">
-        <v>-15.43395342754909</v>
+        <v>-15.433254357843692</v>
       </c>
       <c r="C54">
         <v>339.231271826982</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-11.741652944511516</v>
+        <v>-11.736651706530623</v>
       </c>
       <c r="B55">
-        <v>-14.737969185715603</v>
+        <v>-14.737512243064396</v>
       </c>
       <c r="C55">
         <v>339.231271826982</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-12.251147598347046</v>
+        <v>-12.246188784531203</v>
       </c>
       <c r="B56">
-        <v>-14.028809037500919</v>
+        <v>-14.028590850795331</v>
       </c>
       <c r="C56">
         <v>339.231271826982</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-12.730561330769053</v>
+        <v>-12.725653231097374</v>
       </c>
       <c r="B57">
-        <v>-13.306248092221448</v>
+        <v>-13.306265234698721</v>
       </c>
       <c r="C57">
         <v>339.231271826982</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-13.163068046874834</v>
+        <v>-13.158223610949687</v>
       </c>
       <c r="B58">
-        <v>-12.562790466354075</v>
+        <v>-12.563037604497119</v>
       </c>
       <c r="C58">
         <v>339.231271826982</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-13.566234365522556</v>
+        <v>-13.561461703466216</v>
       </c>
       <c r="B59">
-        <v>-11.806261940605323</v>
+        <v>-11.806735742807652</v>
       </c>
       <c r="C59">
         <v>339.231271826982</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-13.941769802680726</v>
+        <v>-13.937076554218807</v>
       </c>
       <c r="B60">
-        <v>-11.037424089936886</v>
+        <v>-11.038121419661197</v>
       </c>
       <c r="C60">
         <v>339.231271826982</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-14.284727015911077</v>
+        <v>-14.28012219252504</v>
       </c>
       <c r="B61">
-        <v>-10.254072914972749</v>
+        <v>-10.254990075798746</v>
       </c>
       <c r="C61">
         <v>339.231271826982</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-14.590704417643405</v>
+        <v>-14.586198250650899</v>
       </c>
       <c r="B62">
-        <v>-9.45424754553277</v>
+        <v>-9.45538034265304</v>
       </c>
       <c r="C62">
         <v>339.231271826982</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-14.869850708562431</v>
+        <v>-14.865450620040292</v>
       </c>
       <c r="B63">
-        <v>-8.6424691422714819</v>
+        <v>-8.6438145314870862</v>
       </c>
       <c r="C63">
         <v>339.231271826982</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-15.121458667940528</v>
+        <v>-15.117172273513626</v>
       </c>
       <c r="B64">
-        <v>-7.818422644312907</v>
+        <v>-7.8199775002559306</v>
       </c>
       <c r="C64">
         <v>339.231271826982</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-15.344344317267542</v>
+        <v>-15.34017955666612</v>
       </c>
       <c r="B65">
-        <v>-6.9815805992055244</v>
+        <v>-6.9833416606568717</v>
       </c>
       <c r="C65">
         <v>339.231271826982</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-15.529959858585384</v>
+        <v>-15.525927023210073</v>
       </c>
       <c r="B66">
-        <v>-6.1281350349722556</v>
+        <v>-6.1300980651757415</v>
       </c>
       <c r="C66">
         <v>339.231271826982</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-15.687226481579719</v>
+        <v>-15.683333387609297</v>
       </c>
       <c r="B67">
-        <v>-5.2620602664590708</v>
+        <v>-5.26422203752798</v>
       </c>
       <c r="C67">
         <v>339.231271826982</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-15.81504446494891</v>
+        <v>-15.811299220362951</v>
       </c>
       <c r="B68">
-        <v>-4.382866377090993</v>
+        <v>-4.385223530836778</v>
       </c>
       <c r="C68">
         <v>339.231271826982</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-15.912194571318986</v>
+        <v>-15.908605604627459</v>
       </c>
       <c r="B69">
-        <v>-3.4900102068897159</v>
+        <v>-3.4925592393314377</v>
       </c>
       <c r="C69">
         <v>339.231271826982</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-15.977290661836118</v>
+        <v>-15.973866762354033</v>
       </c>
       <c r="B70">
-        <v>-2.582874242673765</v>
+        <v>-2.5856114824746959</v>
       </c>
       <c r="C70">
         <v>339.231271826982</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-16.00873173995517</v>
+        <v>-16.005482109279434</v>
       </c>
       <c r="B71">
-        <v>-1.6607452539703134</v>
+        <v>-1.6636668345137673</v>
       </c>
       <c r="C71">
         <v>339.231271826982</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-16.004652875650667</v>
+        <v>-16.001587189909358</v>
       </c>
       <c r="B72">
-        <v>-0.72279243016462169</v>
+        <v>-0.72589425481236169</v>
       </c>
       <c r="C72">
         <v>339.231271826982</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-15.962876393492129</v>
+        <v>-15.960004875238296</v>
       </c>
       <c r="B73">
-        <v>0.23195436480116272</v>
+        <v>0.22867666470820225</v>
       </c>
       <c r="C73">
         <v>339.231271826982</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-15.88086744641131</v>
+        <v>-15.878200943470588</v>
       </c>
       <c r="B74">
-        <v>1.2046243839404329</v>
+        <v>1.2011754985000898</v>
       </c>
       <c r="C74">
         <v>339.231271826982</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-15.755702421544864</v>
+        <v>-15.75325248722929</v>
       </c>
       <c r="B75">
-        <v>2.1965200721530365</v>
+        <v>2.1929050691910228</v>
       </c>
       <c r="C75">
         <v>339.231271826982</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-15.584065801341701</v>
+        <v>-15.581844765399039</v>
       </c>
       <c r="B76">
-        <v>3.2091184645754982</v>
+        <v>3.2053428508070914</v>
       </c>
       <c r="C76">
         <v>339.231271826982</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-15.362303275787077</v>
+        <v>-15.36032428689224</v>
       </c>
       <c r="B77">
-        <v>4.2440475255326557</v>
+        <v>4.2401173078342493</v>
       </c>
       <c r="C77">
         <v>339.231271826982</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-15.079734240085903</v>
+        <v>-15.078012978292355</v>
       </c>
       <c r="B78">
-        <v>5.3060653744790471</v>
+        <v>5.3019879601181215</v>
       </c>
       <c r="C78">
         <v>339.231271826982</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-14.730801444602436</v>
+        <v>-14.729354600222445</v>
       </c>
       <c r="B79">
-        <v>6.3976477193088295</v>
+        <v>6.3934313809645857</v>
       </c>
       <c r="C79">
         <v>339.231271826982</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-14.305270328713117</v>
+        <v>-14.304116255029065</v>
       </c>
       <c r="B80">
-        <v>7.5233539705559487</v>
+        <v>7.51900866276924</v>
       </c>
       <c r="C80">
         <v>339.231271826982</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-13.808170280036466</v>
+        <v>-13.807323786080211</v>
       </c>
       <c r="B81">
-        <v>8.6809435784078026</v>
+        <v>8.6764796447542114</v>
       </c>
       <c r="C81">
         <v>339.231271826982</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-13.623764375555046</v>
+        <v>-13.623126358575918</v>
       </c>
       <c r="B82">
-        <v>9.6992305793979039</v>
+        <v>9.6946181605383934</v>
       </c>
       <c r="C82">
         <v>339.231271826982</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-12.412996403392167</v>
+        <v>-12.409318206723318</v>
       </c>
       <c r="B1">
-        <v>8.7584300785311537</v>
+        <v>8.7637202703121666</v>
       </c>
       <c r="C1">
         <v>353.47999474773957</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-13.944280007101197</v>
+        <v>-13.943160211860155</v>
       </c>
       <c r="B2">
-        <v>7.1615171726800479</v>
+        <v>7.1675342721779778</v>
       </c>
       <c r="C2">
         <v>353.47999474773957</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-14.847238193928035</v>
+        <v>-14.848002502397307</v>
       </c>
       <c r="B3">
-        <v>5.8629333069678209</v>
+        <v>5.8694013066474113</v>
       </c>
       <c r="C3">
         <v>353.47999474773957</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-15.537691593485244</v>
+        <v>-15.540003094517951</v>
       </c>
       <c r="B4">
-        <v>4.6652467589634208</v>
+        <v>4.6721238935202685</v>
       </c>
       <c r="C4">
         <v>353.47999474773957</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-16.075811684521387</v>
+        <v>-16.079453920108502</v>
       </c>
       <c r="B5">
-        <v>3.5398880978966125</v>
+        <v>3.5471325553815736</v>
       </c>
       <c r="C5">
         <v>353.47999474773957</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-16.499004984513505</v>
+        <v>-16.50383559461514</v>
       </c>
       <c r="B6">
-        <v>2.469096701398751</v>
+        <v>2.4766670121576109</v>
       </c>
       <c r="C6">
         <v>353.47999474773957</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-16.823508670122028</v>
+        <v>-16.829419756781324</v>
       </c>
       <c r="B7">
-        <v>1.4451631545750716</v>
+        <v>1.4530169085646572</v>
       </c>
       <c r="C7">
         <v>353.47999474773957</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-17.070003019418365</v>
+        <v>-17.076918874143036</v>
       </c>
       <c r="B8">
-        <v>0.4582684570460212</v>
+        <v>0.46636759187949212</v>
       </c>
       <c r="C8">
         <v>353.47999474773957</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-17.246189912583013</v>
+        <v>-17.254048834175652</v>
       </c>
       <c r="B9">
-        <v>-0.49524424551861729</v>
+        <v>-0.4869371297973133</v>
       </c>
       <c r="C9">
         <v>353.47999474773957</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-17.358650390428739</v>
+        <v>-17.367401488770774</v>
       </c>
       <c r="B10">
-        <v>-1.4184996326814299</v>
+        <v>-1.4100208213914129</v>
       </c>
       <c r="C10">
         <v>353.47999474773957</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-17.413017006251565</v>
+        <v>-17.422617737223806</v>
       </c>
       <c r="B11">
-        <v>-2.3141720419324963</v>
+        <v>-2.3055564366459955</v>
       </c>
       <c r="C11">
         <v>353.47999474773957</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-17.4141188824379</v>
+        <v>-17.424533158921523</v>
       </c>
       <c r="B12">
-        <v>-3.1845543415969537</v>
+        <v>-3.175835326522233</v>
       </c>
       <c r="C12">
         <v>353.47999474773957</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-17.366104048535384</v>
+        <v>-17.377300796272063</v>
       </c>
       <c r="B13">
-        <v>-4.0316160169767947</v>
+        <v>-4.0228254201869351</v>
       </c>
       <c r="C13">
         <v>353.47999474773957</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-17.272543134332334</v>
+        <v>-17.284495187752245</v>
       </c>
       <c r="B14">
-        <v>-4.8570524038467884</v>
+        <v>-4.8482205213230731</v>
       </c>
       <c r="C14">
         <v>353.47999474773957</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-17.136518232084548</v>
+        <v>-17.149201489279136</v>
       </c>
       <c r="B15">
-        <v>-5.6623268802584761</v>
+        <v>-5.6534825385067444</v>
       </c>
       <c r="C15">
         <v>353.47999474773957</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-16.960700548883004</v>
+        <v>-16.974093325248408</v>
       </c>
       <c r="B16">
-        <v>-6.4487077359006957</v>
+        <v>-6.4398783751095614</v>
       </c>
       <c r="C16">
         <v>353.47999474773957</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-16.747420348233664</v>
+        <v>-16.761502885045193</v>
       </c>
       <c r="B17">
-        <v>-7.2173013803763775</v>
+        <v>-7.2085131446994861</v>
       </c>
       <c r="C17">
         <v>353.47999474773957</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-16.498732703571203</v>
+        <v>-16.513486801682845</v>
       </c>
       <c r="B18">
-        <v>-7.9690835629847019</v>
+        <v>-7.9603613877927621</v>
       </c>
       <c r="C18">
         <v>353.47999474773957</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-16.204693204406947</v>
+        <v>-16.220096152843855</v>
       </c>
       <c r="B19">
-        <v>-8.6993326755332916</v>
+        <v>-8.6907087835414689</v>
       </c>
       <c r="C19">
         <v>353.47999474773957</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-15.876622306327123</v>
+        <v>-15.892657326352266</v>
       </c>
       <c r="B20">
-        <v>-9.413423672716366</v>
+        <v>-9.4049223681477621</v>
       </c>
       <c r="C20">
         <v>353.47999474773957</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-15.516465378402618</v>
+        <v>-15.533116687310317</v>
       </c>
       <c r="B21">
-        <v>-10.112280216178107</v>
+        <v>-10.103924431412111</v>
       </c>
       <c r="C21">
         <v>353.47999474773957</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-15.125477805598472</v>
+        <v>-15.142730235905296</v>
       </c>
       <c r="B22">
-        <v>-10.796498362964053</v>
+        <v>-10.788310132054127</v>
       </c>
       <c r="C22">
         <v>353.47999474773957</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-14.692899599458416</v>
+        <v>-14.710732533640817</v>
       </c>
       <c r="B23">
-        <v>-11.460969268291203</v>
+        <v>-11.452978241064187</v>
       </c>
       <c r="C23">
         <v>353.47999474773957</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-14.224576716377602</v>
+        <v>-14.242972024782498</v>
       </c>
       <c r="B24">
-        <v>-12.108468593486004</v>
+        <v>-12.100700057870451</v>
       </c>
       <c r="C24">
         <v>353.47999474773957</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-13.726363474515336</v>
+        <v>-13.745305649640123</v>
       </c>
       <c r="B25">
-        <v>-12.741775970042266</v>
+        <v>-12.734250907772106</v>
       </c>
       <c r="C25">
         <v>353.47999474773957</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-13.196706666401013</v>
+        <v>-13.216179150249721</v>
       </c>
       <c r="B26">
-        <v>-13.360153934726148</v>
+        <v>-13.352894301882341</v>
       </c>
       <c r="C26">
         <v>353.47999474773957</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-12.617884174153767</v>
+        <v>-12.637859665504236</v>
       </c>
       <c r="B27">
-        <v>-13.955188022238986</v>
+        <v>-13.948227481174371</v>
       </c>
       <c r="C27">
         <v>353.47999474773957</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-12.008134536098142</v>
+        <v>-12.028594722411413</v>
       </c>
       <c r="B28">
-        <v>-14.535537894414752</v>
+        <v>-14.528897080353962</v>
       </c>
       <c r="C28">
         <v>353.47999474773957</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-11.368107893536324</v>
+        <v>-11.389034531991399</v>
       </c>
       <c r="B29">
-        <v>-15.101512238480531</v>
+        <v>-15.095211203482039</v>
       </c>
       <c r="C29">
         <v>353.47999474773957</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-10.673231559669912</v>
+        <v>-10.694589027697983</v>
       </c>
       <c r="B30">
-        <v>-15.6414439375742</v>
+        <v>-15.635517788187336</v>
       </c>
       <c r="C30">
         <v>353.47999474773957</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-9.9396487113525254</v>
+        <v>-9.9614090553482448</v>
       </c>
       <c r="B31">
-        <v>-16.162997775462479</v>
+        <v>-16.157469951733908</v>
       </c>
       <c r="C31">
         <v>353.47999474773957</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-9.1719178616895576</v>
+        <v>-9.19405560982773</v>
       </c>
       <c r="B32">
-        <v>-16.668338135126948</v>
+        <v>-16.663228932554436</v>
       </c>
       <c r="C32">
         <v>353.47999474773957</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-8.34004887679125</v>
+        <v>-8.3625114196663439</v>
       </c>
       <c r="B33">
-        <v>-17.143225694686642</v>
+        <v>-17.138570974128061</v>
       </c>
       <c r="C33">
         <v>353.47999474773957</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-7.456829876199234</v>
+        <v>-7.4795681918109924</v>
       </c>
       <c r="B34">
-        <v>-17.593732255990641</v>
+        <v>-17.589557457659271</v>
       </c>
       <c r="C34">
         <v>353.47999474773957</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-6.5310024170813756</v>
+        <v>-6.55397382466748</v>
       </c>
       <c r="B35">
-        <v>-18.024008312221508</v>
+        <v>-18.020333595917233</v>
       </c>
       <c r="C35">
         <v>353.47999474773957</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-5.5161705661039662</v>
+        <v>-5.5392731895415723</v>
       </c>
       <c r="B36">
-        <v>-18.412025064470424</v>
+        <v>-18.408886514069206</v>
       </c>
       <c r="C36">
         <v>353.47999474773957</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-4.428075104881299</v>
+        <v>-4.4512044228709655</v>
       </c>
       <c r="B37">
-        <v>-18.765256239159825</v>
+        <v>-18.762673766043939</v>
       </c>
       <c r="C37">
         <v>353.47999474773957</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-3.278096004628944</v>
+        <v>-3.3011590094276535</v>
       </c>
       <c r="B38">
-        <v>-19.08910504901726</v>
+        <v>-19.087093234389439</v>
       </c>
       <c r="C38">
         <v>353.47999474773957</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-1.9705634878533445</v>
+        <v>-1.9932639357455595</v>
       </c>
       <c r="B39">
-        <v>-19.338147463559334</v>
+        <v>-19.336715260323437</v>
       </c>
       <c r="C39">
         <v>353.47999474773957</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-0.66303097107774711</v>
+        <v>-0.68536886206346792</v>
       </c>
       <c r="B40">
-        <v>-19.5871898781014</v>
+        <v>-19.586337286257439</v>
       </c>
       <c r="C40">
         <v>353.47999474773957</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>0.64450154569784934</v>
+        <v>0.62252621161861754</v>
       </c>
       <c r="B41">
-        <v>-19.836232292643473</v>
+        <v>-19.835959312191434</v>
       </c>
       <c r="C41">
         <v>353.47999474773957</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>0.722373915045706</v>
+        <v>0.70041205241752358</v>
       </c>
       <c r="B42">
-        <v>-19.799258475292326</v>
+        <v>-19.79905291858238</v>
       </c>
       <c r="C42">
         <v>353.47999474773957</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-0.4147988615120059</v>
+        <v>-0.43709380983730611</v>
       </c>
       <c r="B43">
-        <v>-19.469329220250149</v>
+        <v>-19.468691553647009</v>
       </c>
       <c r="C43">
         <v>353.47999474773957</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-1.5519716380697213</v>
+        <v>-1.5745996720921436</v>
       </c>
       <c r="B44">
-        <v>-19.139399965207982</v>
+        <v>-19.138330188711631</v>
       </c>
       <c r="C44">
         <v>353.47999474773957</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-2.6891444146274393</v>
+        <v>-2.712105534346982</v>
       </c>
       <c r="B45">
-        <v>-18.809470710165812</v>
+        <v>-18.807968823776257</v>
       </c>
       <c r="C45">
         <v>353.47999474773957</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-3.6757746456692515</v>
+        <v>-3.6987738202088547</v>
       </c>
       <c r="B46">
-        <v>-18.408063822837683</v>
+        <v>-18.406132709280595</v>
       </c>
       <c r="C46">
         <v>353.47999474773957</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-4.6038918756889142</v>
+        <v>-4.6268366804056384</v>
       </c>
       <c r="B47">
-        <v>-17.978874950312772</v>
+        <v>-17.976526272412649</v>
       </c>
       <c r="C47">
         <v>353.47999474773957</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-5.4628836552253466</v>
+        <v>-5.48567028469648</v>
       </c>
       <c r="B48">
-        <v>-17.516865299354048</v>
+        <v>-17.51411538557641</v>
       </c>
       <c r="C48">
         <v>353.47999474773957</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-6.2388917287388876</v>
+        <v>-6.2614193483839813</v>
       </c>
       <c r="B49">
-        <v>-17.01545496731541</v>
+        <v>-17.012334688683797</v>
       </c>
       <c r="C49">
         <v>353.47999474773957</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-6.9755190544381538</v>
+        <v>-6.9977455418694188</v>
       </c>
       <c r="B50">
-        <v>-16.495346647928621</v>
+        <v>-16.49187336961452</v>
       </c>
       <c r="C50">
         <v>353.47999474773957</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-7.6648232848081372</v>
+        <v>-7.6867003146582817</v>
       </c>
       <c r="B51">
-        <v>-15.952769312922444</v>
+        <v>-15.948964988536096</v>
       </c>
       <c r="C51">
         <v>353.47999474773957</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-8.295716579461109</v>
+        <v>-8.31719253309564</v>
       </c>
       <c r="B52">
-        <v>-15.382458453347837</v>
+        <v>-15.3783539850021</v>
       </c>
       <c r="C52">
         <v>353.47999474773957</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-8.89580666581858</v>
+        <v>-8.91685665004137</v>
       </c>
       <c r="B53">
-        <v>-14.79752222399336</v>
+        <v>-14.793135011184937</v>
       </c>
       <c r="C53">
         <v>353.47999474773957</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-9.4610884955592365</v>
+        <v>-9.4816852311400712</v>
       </c>
       <c r="B54">
-        <v>-14.196059027073368</v>
+        <v>-14.19140913464495</v>
       </c>
       <c r="C54">
         <v>353.47999474773957</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-9.97772060282042</v>
+        <v>-9.9978295397477677</v>
       </c>
       <c r="B55">
-        <v>-13.57149693168394</v>
+        <v>-13.566614098104976</v>
       </c>
       <c r="C55">
         <v>353.47999474773957</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-10.467851243764295</v>
+        <v>-10.487454792362524</v>
       </c>
       <c r="B56">
-        <v>-12.934351934511</v>
+        <v>-12.92925294288956</v>
       </c>
       <c r="C56">
         <v>353.47999474773957</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-10.931003072703774</v>
+        <v>-10.95008360347191</v>
       </c>
       <c r="B57">
-        <v>-12.284397391721877</v>
+        <v>-12.279099458721653</v>
       </c>
       <c r="C57">
         <v>353.47999474773957</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-11.351932722006536</v>
+        <v>-11.370464134906886</v>
       </c>
       <c r="B58">
-        <v>-11.614395749157458</v>
+        <v>-11.608926525280612</v>
       </c>
       <c r="C58">
         <v>353.47999474773957</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-11.746361414779049</v>
+        <v>-11.764328006857372</v>
       </c>
       <c r="B59">
-        <v>-10.931811446856523</v>
+        <v>-10.926188608755439</v>
       </c>
       <c r="C59">
         <v>353.47999474773957</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-12.115802957724556</v>
+        <v>-12.133190069703883</v>
       </c>
       <c r="B60">
-        <v>-10.23736324056029</v>
+        <v>-10.231603524654425</v>
       </c>
       <c r="C60">
         <v>353.47999474773957</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-12.455728834095902</v>
+        <v>-12.472519413904433</v>
       </c>
       <c r="B61">
-        <v>-9.52890098956438</v>
+        <v>-9.5230242905575562</v>
       </c>
       <c r="C61">
         <v>353.47999474773957</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-12.762059109436708</v>
+        <v>-12.778233922643349</v>
       </c>
       <c r="B62">
-        <v>-8.8044875401304683</v>
+        <v>-8.7985165855611616</v>
       </c>
       <c r="C62">
         <v>353.47999474773957</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-13.043963954113471</v>
+        <v>-13.059508941298287</v>
       </c>
       <c r="B63">
-        <v>-8.0684768910780225</v>
+        <v>-8.06242816921349</v>
       </c>
       <c r="C63">
         <v>353.47999474773957</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-13.300769725945346</v>
+        <v>-13.315670313104153</v>
       </c>
       <c r="B64">
-        <v>-7.3205491969578338</v>
+        <v>-7.31443959070459</v>
       </c>
       <c r="C64">
         <v>353.47999474773957</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-13.531361374220015</v>
+        <v>-13.545602134957358</v>
       </c>
       <c r="B65">
-        <v>-6.5601750314570859</v>
+        <v>-6.5540220766560378</v>
       </c>
       <c r="C65">
         <v>353.47999474773957</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-13.727875769441004</v>
+        <v>-13.741435943220187</v>
       </c>
       <c r="B66">
-        <v>-5.783620979036403</v>
+        <v>-5.7774471365856961</v>
       </c>
       <c r="C66">
         <v>353.47999474773957</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-13.898433419488814</v>
+        <v>-13.911296442077843</v>
       </c>
       <c r="B67">
-        <v>-4.9947426585460493</v>
+        <v>-4.988564681177464</v>
       </c>
       <c r="C67">
         <v>353.47999474773957</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-14.042008646226009</v>
+        <v>-14.05415657189338</v>
       </c>
       <c r="B68">
-        <v>-4.1930530777905624</v>
+        <v>-4.1868880357439773</v>
       </c>
       <c r="C68">
         <v>353.47999474773957</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-14.157469811545328</v>
+        <v>-14.168882976035333</v>
       </c>
       <c r="B69">
-        <v>-3.3780149347585104</v>
+        <v>-3.3718801565105068</v>
       </c>
       <c r="C69">
         <v>353.47999474773957</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-14.243540335760214</v>
+        <v>-14.254196898774621</v>
       </c>
       <c r="B70">
-        <v>-2.5490221091461169</v>
+        <v>-2.5429351019890625</v>
       </c>
       <c r="C70">
         <v>353.47999474773957</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-14.29876048258417</v>
+        <v>-14.30863582082128</v>
       </c>
       <c r="B71">
-        <v>-1.7053815178574163</v>
+        <v>-1.6993598538848849</v>
       </c>
       <c r="C71">
         <v>353.47999474773957</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-14.321449906467304</v>
+        <v>-14.330515814944704</v>
       </c>
       <c r="B72">
-        <v>-0.84629533247176492</v>
+        <v>-0.84035647921626344</v>
       </c>
       <c r="C72">
         <v>353.47999474773957</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-14.309672751577182</v>
+        <v>-14.3178963951447</v>
       </c>
       <c r="B73">
-        <v>0.029155591767390625</v>
+        <v>0.034994525990582684</v>
       </c>
       <c r="C73">
         <v>353.47999474773957</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-14.261209607320236</v>
+        <v>-14.268552145291753</v>
       </c>
       <c r="B74">
-        <v>0.92202503147685322</v>
+        <v>0.92774768053878376</v>
       </c>
       <c r="C74">
         <v>353.47999474773957</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-14.173544493851292</v>
+        <v>-14.179959278689768</v>
       </c>
       <c r="B75">
-        <v>1.8335075744164873</v>
+        <v>1.8390988868444347</v>
       </c>
       <c r="C75">
         <v>353.47999474773957</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-14.043881260456391</v>
+        <v>-14.049311488309142</v>
       </c>
       <c r="B76">
-        <v>2.764930833533608</v>
+        <v>2.7703779202654246</v>
       </c>
       <c r="C76">
         <v>353.47999474773957</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-13.869213941055548</v>
+        <v>-13.873589613139863</v>
       </c>
       <c r="B77">
-        <v>3.7177220421554646</v>
+        <v>3.7230154175318861</v>
       </c>
       <c r="C77">
         <v>353.47999474773957</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-13.640461418576861</v>
+        <v>-13.643682353230497</v>
       </c>
       <c r="B78">
-        <v>4.6961929165785135</v>
+        <v>4.7013287901123082</v>
       </c>
       <c r="C78">
         <v>353.47999474773957</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-13.353384791487503</v>
+        <v>-13.355318420594537</v>
       </c>
       <c r="B79">
-        <v>5.702356088142424</v>
+        <v>5.7073419981261484</v>
       </c>
       <c r="C79">
         <v>353.47999474773957</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-13.000117869599738</v>
+        <v>-13.000562637373873</v>
       </c>
       <c r="B80">
-        <v>6.7399464256034367</v>
+        <v>6.7448151447498645</v>
       </c>
       <c r="C80">
         <v>353.47999474773957</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-12.586189812328323</v>
+        <v>-12.584835075660251</v>
       </c>
       <c r="B81">
-        <v>7.8063386829080494</v>
+        <v>7.8111799157436019</v>
       </c>
       <c r="C81">
         <v>353.47999474773957</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-12.412996403392167</v>
+        <v>-12.409318206723318</v>
       </c>
       <c r="B82">
-        <v>8.7584300785311537</v>
+        <v>8.7637202703121666</v>
       </c>
       <c r="C82">
         <v>353.47999474773957</v>
